--- a/HV Module Test/hv_module_test_results.xlsx
+++ b/HV Module Test/hv_module_test_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,251 @@
         </is>
       </c>
       <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>lke</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>09/11/2026</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12:14:03 PM</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>E08F2</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7200489</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>07.52</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
